--- a/data/hotdog_tracker.xlsx
+++ b/data/hotdog_tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e4b65587e77f2723/Desktop/Bit Stuff/hotdog_bit/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="32" documentId="13_ncr:1_{7392CE9E-C5AE-4732-9F7D-3C8C18A30E00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8031BD3B-5B9D-4163-BF36-3F48CCF14D97}"/>
+  <xr:revisionPtr revIDLastSave="49" documentId="13_ncr:1_{7392CE9E-C5AE-4732-9F7D-3C8C18A30E00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{44770FA6-4E62-4124-946B-80DE7FA1607C}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="104">
   <si>
     <t>Date</t>
   </si>
@@ -334,6 +334,9 @@
   </si>
   <si>
     <t>5:33pm</t>
+  </si>
+  <si>
+    <t>6:03pm</t>
   </si>
 </sst>
 </file>
@@ -388,6 +391,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -653,7 +660,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q63"/>
+  <dimension ref="A1:Q64"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.5546875" bestFit="1" customWidth="1"/>
@@ -918,7 +925,7 @@
         <v>0</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P5">
         <v>1</v>
@@ -3837,6 +3844,56 @@
       </c>
       <c r="P63">
         <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A64" s="1">
+        <v>46105</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C64" t="s">
+        <v>8</v>
+      </c>
+      <c r="D64">
+        <v>3</v>
+      </c>
+      <c r="E64" t="s">
+        <v>5</v>
+      </c>
+      <c r="F64">
+        <v>0</v>
+      </c>
+      <c r="G64">
+        <v>1</v>
+      </c>
+      <c r="H64">
+        <v>0</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>0</v>
+      </c>
+      <c r="K64">
+        <v>0</v>
+      </c>
+      <c r="L64">
+        <v>0</v>
+      </c>
+      <c r="M64">
+        <v>0</v>
+      </c>
+      <c r="N64">
+        <v>0</v>
+      </c>
+      <c r="O64">
+        <v>0</v>
+      </c>
+      <c r="P64">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/data/hotdog_tracker.xlsx
+++ b/data/hotdog_tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e4b65587e77f2723/Desktop/Bit Stuff/hotdog_bit/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="49" documentId="13_ncr:1_{7392CE9E-C5AE-4732-9F7D-3C8C18A30E00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{44770FA6-4E62-4124-946B-80DE7FA1607C}"/>
+  <xr:revisionPtr revIDLastSave="65" documentId="13_ncr:1_{7392CE9E-C5AE-4732-9F7D-3C8C18A30E00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8C5415A8-A4B5-4CB9-A7AE-3461C145C933}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="105">
   <si>
     <t>Date</t>
   </si>
@@ -337,6 +337,9 @@
   </si>
   <si>
     <t>6:03pm</t>
+  </si>
+  <si>
+    <t>5:14pm</t>
   </si>
 </sst>
 </file>
@@ -660,7 +663,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q64"/>
+  <dimension ref="A1:Q65"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.5546875" bestFit="1" customWidth="1"/>
@@ -3896,6 +3899,56 @@
         <v>1</v>
       </c>
     </row>
+    <row r="65" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A65" s="1">
+        <v>46106</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="C65" t="s">
+        <v>13</v>
+      </c>
+      <c r="D65">
+        <v>2</v>
+      </c>
+      <c r="E65" t="s">
+        <v>9</v>
+      </c>
+      <c r="F65">
+        <v>1</v>
+      </c>
+      <c r="G65">
+        <v>0</v>
+      </c>
+      <c r="H65">
+        <v>0</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>0</v>
+      </c>
+      <c r="K65">
+        <v>0</v>
+      </c>
+      <c r="L65">
+        <v>0</v>
+      </c>
+      <c r="M65">
+        <v>0</v>
+      </c>
+      <c r="N65">
+        <v>0</v>
+      </c>
+      <c r="O65">
+        <v>0</v>
+      </c>
+      <c r="P65">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
